--- a/output/pdf_financials_xlsx/BCF.xlsx
+++ b/output/pdf_financials_xlsx/BCF.xlsx
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.239189</v>
+        <v>0.6896330000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.24308</v>
+        <v>0.79306</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.236347</v>
+        <v>0.678278</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.253249</v>
+        <v>0.982667</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.276056</v>
+        <v>1.504554</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.28677</v>
+        <v>1.476044</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.291413</v>
+        <v>0.73114</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.292944</v>
+        <v>1.050794</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.315137</v>
+        <v>1.381684</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.331851</v>
+        <v>1.910879</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.427561</v>
+        <v>3.822413</v>
       </c>
     </row>
     <row r="11">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.297034</v>
+        <v>2.84659</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>3.53286</v>
+        <v>2.98288</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.161175</v>
+        <v>2.719244</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.111612</v>
+        <v>2.382194</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.153209</v>
+        <v>1.924711</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.634908</v>
+        <v>1.445634</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.76975</v>
+        <v>2.330023</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>3.466029</v>
+        <v>2.708179</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4.360005</v>
+        <v>3.293458</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>4.857281</v>
+        <v>3.278253</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>7.172835</v>
+        <v>3.777983</v>
       </c>
     </row>
     <row r="12">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.256949</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005494</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.930009</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.393606</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000596</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001924</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005728</v>
       </c>
     </row>
     <row r="35">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.256949</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005494</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.930009</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.393606</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000596</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001924</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005728</v>
       </c>
     </row>
     <row r="37">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -27366,7 +27366,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -29130,7 +29130,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E292" s="5" t="n">
@@ -31034,7 +31034,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E317" s="5" t="n">
